--- a/data/trans_camb/IP04D$colectiva-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,04</t>
+          <t>-5,75; 2,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 6,6</t>
+          <t>-4,12; 6,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,89</t>
+          <t>-4,5; 1,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,89</t>
+          <t>-0,2; 9,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,23</t>
+          <t>-4,07; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,57</t>
+          <t>-0,83; 6,57</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,14; 118,31</t>
+          <t>-72,12; 89,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 167,55</t>
+          <t>-54,24; 188,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 190,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 628,9</t>
+          <t>-18,51; 654,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 39,88</t>
+          <t>-71,05; 43,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 227,91</t>
+          <t>-18,4; 210,72</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,67</t>
+          <t>-1,67; 3,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,82</t>
+          <t>1,95; 9,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,45</t>
+          <t>-2,87; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,16</t>
+          <t>-0,81; 6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,37</t>
+          <t>-1,51; 2,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,84</t>
+          <t>1,15; 6,62</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 328,31</t>
+          <t>-50,35; 275,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,8; 650,7</t>
+          <t>29,83; 712,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,21; 113,94</t>
+          <t>-60,72; 142,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 290,95</t>
+          <t>-21,4; 272,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 120,97</t>
+          <t>-38,54; 103,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,05; 320,85</t>
+          <t>24,82; 304,08</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,48</t>
+          <t>-3,11; 3,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,34</t>
+          <t>0,63; 9,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,43</t>
+          <t>-3,56; 2,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,69</t>
+          <t>1,59; 9,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,13</t>
+          <t>-2,36; 2,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,99</t>
+          <t>2,45; 8,1</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 239,24</t>
+          <t>-63,39; 204,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,52; 520,53</t>
+          <t>0,73; 544,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,76; 159,77</t>
+          <t>-75,6; 186,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 612,79</t>
+          <t>23,37; 598,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 113,89</t>
+          <t>-54,13; 108,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,65; 403,82</t>
+          <t>49,01; 408,87</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,8</t>
+          <t>-3,78; 2,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,04</t>
+          <t>0,61; 8,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,34</t>
+          <t>1,53; 8,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,87</t>
+          <t>2,6; 8,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,68</t>
+          <t>-0,35; 4,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,0</t>
+          <t>2,44; 7,06</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 175,18</t>
+          <t>-72,24; 192,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 466,88</t>
+          <t>7,97; 465,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,02; 1632,79</t>
+          <t>21,64; 1767,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54,69; 1670,37</t>
+          <t>52,81; 1482,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 328,18</t>
+          <t>-14,91; 299,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,12; 487,71</t>
+          <t>52,94; 475,08</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,66</t>
+          <t>-1,6; 1,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,73</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,21</t>
+          <t>-0,69; 2,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,01</t>
+          <t>2,38; 6,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,52</t>
+          <t>-0,73; 1,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,64</t>
+          <t>2,77; 5,67</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 63,35</t>
+          <t>-36,91; 63,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>52,26; 235,81</t>
+          <t>47,36; 232,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 97,73</t>
+          <t>-20,63; 107,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54,51; 283,88</t>
+          <t>62,03; 279,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 60,75</t>
+          <t>-19,49; 55,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,71; 211,51</t>
+          <t>77,47; 219,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,51</t>
+          <t>-5,68; 2,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 6,42</t>
+          <t>-4,0; 7,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,41</t>
+          <t>-4,14; 1,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 9,77</t>
+          <t>-0,06; 10,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,09</t>
+          <t>-3,95; 1,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,57</t>
+          <t>-0,56; 6,75</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,12; 89,41</t>
+          <t>-70,51; 86,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 188,98</t>
+          <t>-56,06; 198,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 654,64</t>
+          <t>-16,39; 599,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 43,87</t>
+          <t>-71,22; 46,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 210,72</t>
+          <t>-15,84; 211,56</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,83</t>
+          <t>-1,59; 3,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 9,33</t>
+          <t>2,38; 9,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,54</t>
+          <t>-2,77; 2,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,02</t>
+          <t>-0,9; 5,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,18</t>
+          <t>-1,51; 2,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,62</t>
+          <t>1,28; 6,68</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 275,45</t>
+          <t>-47,68; 330,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,83; 712,96</t>
+          <t>41,7; 720,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 142,69</t>
+          <t>-59,23; 114,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 272,34</t>
+          <t>-22,0; 263,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 103,4</t>
+          <t>-39,74; 110,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,82; 304,08</t>
+          <t>29,35; 316,02</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,36</t>
+          <t>-3,51; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,5</t>
+          <t>1,19; 9,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,45</t>
+          <t>-3,71; 2,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,71</t>
+          <t>1,47; 9,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,16</t>
+          <t>-2,38; 2,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,1</t>
+          <t>2,48; 8,1</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 204,25</t>
+          <t>-67,13; 201,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 544,73</t>
+          <t>6,62; 612,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,6; 186,42</t>
+          <t>-77,06; 164,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,37; 598,74</t>
+          <t>15,28; 607,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 108,57</t>
+          <t>-55,29; 113,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,01; 408,87</t>
+          <t>53,63; 401,73</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,87</t>
+          <t>-3,6; 2,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,2</t>
+          <t>0,52; 8,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,62</t>
+          <t>1,5; 8,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,11</t>
+          <t>2,26; 8,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,7</t>
+          <t>-0,17; 4,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,06</t>
+          <t>2,16; 6,99</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,24; 192,86</t>
+          <t>-72,91; 199,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 465,57</t>
+          <t>-0,3; 424,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,64; 1767,28</t>
+          <t>33,94; 1649,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,81; 1482,63</t>
+          <t>56,53; 1310,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 299,51</t>
+          <t>-10,96; 291,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,94; 475,08</t>
+          <t>51,59; 541,68</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,7</t>
+          <t>-1,6; 1,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,59</t>
+          <t>2,27; 6,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,29</t>
+          <t>-0,65; 2,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,22</t>
+          <t>2,19; 5,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,47</t>
+          <t>-0,61; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,67</t>
+          <t>2,93; 5,72</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 63,78</t>
+          <t>-36,68; 69,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47,36; 232,28</t>
+          <t>50,18; 236,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 107,8</t>
+          <t>-19,65; 110,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62,03; 279,0</t>
+          <t>60,33; 277,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 55,22</t>
+          <t>-17,33; 59,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,47; 219,1</t>
+          <t>74,45; 210,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Edad-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,08</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,83</t>
+          <t>-4,58; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 7,19</t>
+          <t>-0,41; 8,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,86</t>
+          <t>-5,76; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,38</t>
+          <t>-3,96; 6,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,04</t>
+          <t>-3,96; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,75</t>
+          <t>-1,22; 5,65</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-42,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-28,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17,62%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-42,38%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147,86%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 86,65</t>
+          <t>-100,0; 190,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,06; 198,33</t>
+          <t>-22,91; 531,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,14; 118,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 599,78</t>
+          <t>-56,6; 165,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 46,74</t>
+          <t>-70,32; 39,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 211,56</t>
+          <t>-23,83; 201,88</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,55</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>3,87</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,79</t>
+          <t>-2,83; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,45</t>
+          <t>-1,06; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,61</t>
+          <t>-1,7; 3,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,93</t>
+          <t>2,53; 10,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,36</t>
+          <t>-1,44; 2,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,68</t>
+          <t>1,24; 6,99</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-4,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56,87%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>43,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>228,18%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,87%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>244,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>130,27%</t>
+          <t>129,99%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 330,74</t>
+          <t>-61,21; 113,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,7; 720,47</t>
+          <t>-28,43; 262,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 114,14</t>
+          <t>-50,43; 328,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 263,92</t>
+          <t>51,6; 700,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 110,84</t>
+          <t>-37,51; 120,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,35; 316,02</t>
+          <t>20,54; 302,53</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,42</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,19</t>
+          <t>-3,5; 2,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 9,6</t>
+          <t>1,32; 9,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,46</t>
+          <t>-3,34; 3,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 9,78</t>
+          <t>1,55; 9,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,03</t>
+          <t>-2,18; 2,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,1</t>
+          <t>1,91; 8,09</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-9,44%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>178,74%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>148,17%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,44%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179,48%</t>
+          <t>151,42%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>163,89%</t>
+          <t>164,89%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,13; 201,46</t>
+          <t>-72,76; 159,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,62; 612,12</t>
+          <t>4,61; 614,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,06; 164,87</t>
+          <t>-66,06; 239,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,28; 607,79</t>
+          <t>18,36; 528,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 113,16</t>
+          <t>-52,33; 113,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,63; 401,73</t>
+          <t>37,33; 407,58</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,45</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,94</t>
+          <t>1,55; 8,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,05</t>
+          <t>2,44; 7,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,58</t>
+          <t>-3,67; 2,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,16</t>
+          <t>1,7; 9,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,57</t>
+          <t>0,1; 4,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,99</t>
+          <t>2,84; 7,53</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>326,15%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>354,34%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-10,66%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>131,47%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>326,15%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>350,72%</t>
+          <t>166,1%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>197,9%</t>
+          <t>221,57%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,91; 199,04</t>
+          <t>44,02; 1632,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 424,78</t>
+          <t>56,63; 1690,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,94; 1649,14</t>
+          <t>-69,66; 175,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,53; 1310,87</t>
+          <t>21,55; 535,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 291,91</t>
+          <t>-4,16; 328,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,59; 541,68</t>
+          <t>68,15; 541,11</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,43</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,81</t>
+          <t>-0,88; 2,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,56</t>
+          <t>2,1; 5,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,25</t>
+          <t>-1,47; 1,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,91</t>
+          <t>2,84; 7,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,55</t>
+          <t>-0,79; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,72</t>
+          <t>3,05; 5,84</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>143,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-0,99%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>123,79%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148,91%</t>
+          <t>140,44%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>134,77%</t>
+          <t>141,43%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 69,46</t>
+          <t>-26,99; 97,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50,18; 236,95</t>
+          <t>53,57; 282,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 110,08</t>
+          <t>-36,12; 63,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60,33; 277,57</t>
+          <t>65,51; 258,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 59,2</t>
+          <t>-21,67; 60,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,45; 210,8</t>
+          <t>79,73; 221,19</t>
         </is>
       </c>
     </row>
